--- a/output/full_scan/batch_seq4_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq4_2026-06-12.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1273.133007683394</v>
+        <v>1293.133007683394</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>19.8</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.68093285835155</v>
+        <v>58.68093291087338</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.44759605425601</v>
+        <v>23.44759612368165</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.313300768339379</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0814601262012313</v>
+        <v>0.08146012616307249</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1256.124912459697</v>
+        <v>1271.124912459697</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>221</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.21318572880946</v>
+        <v>69.21318579038018</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33.65175350797271</v>
+        <v>33.65175356774805</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.112491245969735</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.061530904123267</v>
+        <v>2.061530902978521</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1139.184668975975</v>
+        <v>1154.184668975975</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>29.05</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>77.88955768338457</v>
+        <v>77.8895577396578</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>36.03900509192464</v>
+        <v>36.0390052465699</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.918466897597509</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8181961522690426</v>
+        <v>0.8181961521545658</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.03219297938191</v>
+        <v>57.03219292053315</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.79568966563352</v>
+        <v>16.7956896552998</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.985496037185362</v>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>58.9</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>77.64941802584114</v>
+        <v>77.64941795323108</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.52323048165385</v>
+        <v>25.52323056458618</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5.907172807387522</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7098513086775509</v>
+        <v>0.7098513085726115</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1066.749181912294</v>
+        <v>1081.749181912294</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>138.5</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.11497585332667</v>
+        <v>70.11497594111944</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46.21851698151881</v>
+        <v>46.2185171311163</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.674918191229379</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8731883043538762</v>
+        <v>0.8731883034571508</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1052.505448814274</v>
+        <v>1067.505448814274</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>24.65</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.77242827963602</v>
+        <v>62.77242819683774</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>32.0580532217067</v>
+        <v>32.05805317544891</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.250544881427366</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0111657657260021</v>
+        <v>0.0111657656878405</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1022.366082365465</v>
+        <v>1037.366082365465</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>41.4</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>81.9790160882193</v>
+        <v>81.97901610590768</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45.67255819010273</v>
+        <v>45.67255821156888</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.736608236546493</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.9261138150089616</v>
+        <v>0.926113814980343</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.11313373964226</v>
+        <v>58.11313373171714</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.36110824704458</v>
+        <v>29.3611082395064</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.586003763536814</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1912705806547465</v>
+        <v>-0.1912705806738264</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62.36423094907347</v>
+        <v>62.36423095422121</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.7057130085422</v>
+        <v>27.70571303038734</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>4.265305675704626</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-2.152907781128967</v>
+        <v>-2.152907781415195</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>946.512038062462</v>
+        <v>961.512038062462</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>61.4</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>74.4502762715846</v>
+        <v>74.4502764129674</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.16718415306162</v>
+        <v>24.16718452339155</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>3.151203806246196</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.522584184678428</v>
+        <v>1.522584184057153</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>935.0397899137326</v>
+        <v>950.0397899137326</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>293</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.28804647143029</v>
+        <v>64.28804647879464</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.69589168211095</v>
+        <v>35.69589188356471</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.003978991373268</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.996164180729167</v>
+        <v>-1.996164181301556</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>903.6672206779951</v>
+        <v>918.6672206779951</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>25.2</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>70.62303009280083</v>
+        <v>70.62303016350818</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.39943957892068</v>
+        <v>27.39943969345648</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.866722067799524</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.457485309699176</v>
+        <v>0.4574853095560802</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>896.1949165035398</v>
+        <v>911.1949165035398</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>60.4</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.41522481751633</v>
+        <v>60.41522482263358</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.70044960373909</v>
+        <v>28.70044961300982</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.119491650353986</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.1468190219489198</v>
+        <v>-0.1468190220061638</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3624</v>
+        <v>3441</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光頡</t>
+          <t>聯一光</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>883.1311690713437</v>
+        <v>896.2622690513589</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.42268888612847</v>
+        <v>71.77304476105041</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.57524312389832</v>
+        <v>57.8952658767817</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.31311690713437</v>
+        <v>3.12622690513589</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.4263238172645316</v>
+        <v>1.247124064821503</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3652</v>
+        <v>3322</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>精聯</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>881.3790589715335</v>
+        <v>893.906089629496</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>35.55</v>
+        <v>15.35</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.6160758585769</v>
+        <v>62.19113363097252</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.06416631483849</v>
+        <v>25.85589956132609</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.637905897153348</v>
+        <v>1.8906089629496</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1125873984351226</v>
+        <v>0.1981014652842831</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3441</v>
+        <v>3311</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯一光</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>881.2622690513589</v>
+        <v>892.5341509856634</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>70</v>
+        <v>37.55</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>71.77304473649279</v>
+        <v>58.05022393240035</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>57.89526585908253</v>
+        <v>33.21751603302608</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.12622690513589</v>
+        <v>0.2534150985663384</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.247124065174477</v>
+        <v>-0.0061791269047217</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3322</v>
+        <v>3652</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>精聯</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>878.906089629496</v>
+        <v>891.3790589715335</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.35</v>
+        <v>35.55</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62.19113356816374</v>
+        <v>62.61607593315465</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.85589934242296</v>
+        <v>32.06416641462918</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.8906089629496</v>
+        <v>1.637905897153348</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1981014654082981</v>
+        <v>-0.1125873986831558</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3311</v>
+        <v>3703</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>欣陸</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>867.5341509856634</v>
+        <v>884.2427602748891</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.55</v>
+        <v>22.05</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.0502238876456</v>
+        <v>67.46574712296284</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.21751597326734</v>
+        <v>31.20399112074622</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2534150985663384</v>
+        <v>1.424276027488912</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.006179126771167</v>
+        <v>0.2028787283888191</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3236</v>
+        <v>3624</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>千如</t>
+          <t>光頡</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>862.8764611305708</v>
+        <v>883.1311690713437</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>63.2</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.55717640598854</v>
+        <v>68.42268889109445</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.18677728565321</v>
+        <v>32.57524322427466</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7876461130570737</v>
+        <v>1.31311690713437</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0208063769752602</v>
+        <v>-0.426323817379</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3130</v>
+        <v>3236</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>千如</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>860.6393845971004</v>
+        <v>877.8764611305708</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>224</v>
+        <v>63.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>66.03320766680127</v>
+        <v>69.5571764102325</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.02044130397737</v>
+        <v>37.18677724689051</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.063938459710041</v>
+        <v>0.7876461130570737</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2605433191839323</v>
+        <v>-0.0208063769943391</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3703</v>
+        <v>3130</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>欣陸</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>859.2427602748891</v>
+        <v>875.6393845971004</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>22.05</v>
+        <v>224</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>67.46574700528751</v>
+        <v>66.03320817877739</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.20399096556966</v>
+        <v>21.0204415563882</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.424276027488912</v>
+        <v>1.063938459710041</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2028787285223767</v>
+        <v>0.2605433183253569</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
         <v>68.11744727299319</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>52.40610028284171</v>
+        <v>52.40610039143489</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.7114298017062747</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.970951747602701</v>
+        <v>-0.9709517482514052</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3684</v>
+        <v>3321</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>榮昌</t>
+          <t>同泰</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>853.9340137351995</v>
+        <v>856.3770750241929</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>62</v>
+        <v>20.45</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.18372154761742</v>
+        <v>61.01430688721646</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.15052441557279</v>
+        <v>31.25561894469438</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8934013735199536</v>
+        <v>0.6377075024192901</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.066051031835899</v>
+        <v>0.0810854136820833</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3617</v>
+        <v>3684</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>榮昌</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>838.6419396819894</v>
+        <v>853.9340137351995</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.08043106655171</v>
+        <v>57.18372000875411</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.81338706234972</v>
+        <v>14.15052342888941</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8641939681989373</v>
+        <v>0.8934013735199536</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>2</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.3804215892897913</v>
+        <v>0.0660510401068329</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3264</v>
+        <v>3617</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>838.0822785317663</v>
+        <v>838.6419396819894</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>227.5</v>
+        <v>217</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.70867780042105</v>
+        <v>61.08043105106505</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.48141948932859</v>
+        <v>31.81338704668351</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8082278531766269</v>
+        <v>0.8641939681989373</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-2.292301765078775</v>
+        <v>-0.3804215904345795</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3321</v>
+        <v>3264</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>同泰</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>831.3770750241929</v>
+        <v>838.0822785317663</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>20.45</v>
+        <v>227.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,29 +1930,29 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.01430687927515</v>
+        <v>53.70867781011608</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.25561872201908</v>
+        <v>21.48141970402873</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6377075024192901</v>
+        <v>0.8082278531766269</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0810854138026284</v>
+        <v>-2.292301765632066</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>822.5191890807315</v>
+        <v>837.5191890807315</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>79.3</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>63.78865496002265</v>
+        <v>63.78865497017363</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27.71187392334286</v>
+        <v>27.71187395074672</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.751918908073148</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7710088972720297</v>
+        <v>0.7710088969285991</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3268</v>
+        <v>3685</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>海德威</t>
+          <t>元創精密</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>803.7706841127313</v>
+        <v>806.6060798379707</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>19.9</v>
+        <v>30.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.65983963143331</v>
+        <v>59.1731236839195</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.96697564477418</v>
+        <v>12.34668708038338</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3770684112731203</v>
+        <v>1.660607983797065</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0513304049868095</v>
+        <v>0.3813858411275163</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3374</v>
+        <v>3268</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>精材</t>
+          <t>海德威</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>792.6767946640821</v>
+        <v>803.7706841127313</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>233</v>
+        <v>19.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.37486721706289</v>
+        <v>59.65983949921056</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.67255560830675</v>
+        <v>38.96697567223426</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2676794664082044</v>
+        <v>0.3770684112731203</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>3</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-5.71494551006364</v>
+        <v>0.0513304050345062</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3685</v>
+        <v>3374</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>元創精密</t>
+          <t>精材</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>791.6060798379707</v>
+        <v>792.6767946640821</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30.8</v>
+        <v>233</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.17312360554088</v>
+        <v>48.37486724559424</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12.34668702243511</v>
+        <v>20.67255583056543</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.660607983797065</v>
+        <v>0.2676794664082044</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,11 +2160,11 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3813858412896929</v>
+        <v>-5.714945511303791</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.02516527451174</v>
+        <v>48.02516527066759</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.1913729872919</v>
+        <v>27.19137303136496</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.8091131376100725</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-109.3356102665986</v>
+        <v>-109.3356102713689</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.2614616961929</v>
+        <v>51.26146170509831</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30.53529919358087</v>
+        <v>30.5352993402953</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.7215682543990261</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.721888842985895</v>
+        <v>-1.721888843262542</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.18565826643702</v>
+        <v>56.18565826522551</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.67104100950828</v>
+        <v>26.67104104037445</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.8706756439648402</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-8.493848234237234</v>
+        <v>-8.493848234332638</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.95633241353283</v>
+        <v>61.956332529929</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.51438809678023</v>
+        <v>23.51438829416414</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.7456898174683195</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3741937232822999</v>
+        <v>0.3741937228053186</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2382,21 +2382,21 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3592</v>
+        <v>3360</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎</t>
+          <t>尚立</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>766.0761515890878</v>
+        <v>768.8439973951328</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>272</v>
+        <v>15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.73521304917728</v>
+        <v>56.59114397543563</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.10885070160516</v>
+        <v>20.21975156551429</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.60761515890878</v>
+        <v>1.384399739513276</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.401357267556297</v>
+        <v>0.0356595834534404</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3131</v>
+        <v>3520</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>華盈</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>758.8965581429362</v>
+        <v>768.3141852438871</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3230</v>
+        <v>17.05</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.40733892458029</v>
+        <v>59.19701381064951</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.11411106817007</v>
+        <v>39.57607758438195</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8896558142936207</v>
+        <v>0.8314185243887148</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-13.51242765645384</v>
+        <v>0.2565614974465158</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3360</v>
+        <v>3592</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>尚立</t>
+          <t>瑞鼎</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>753.8439973951328</v>
+        <v>766.0761515890878</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56.59114388572431</v>
+        <v>54.73521308983318</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.21975146107021</v>
+        <v>20.10885074313959</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.384399739513276</v>
+        <v>0.60761515890878</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0356595835488379</v>
+        <v>-2.401357269368861</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3520</v>
+        <v>3131</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>華盈</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>753.3141852438871</v>
+        <v>758.8965581429362</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>17.05</v>
+        <v>3230</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,29 +2566,29 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.19701371162535</v>
+        <v>54.40733893311092</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>39.57607722561815</v>
+        <v>19.11411121836155</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8314185243887148</v>
+        <v>0.8896558142936207</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2565614976182301</v>
+        <v>-13.51242766294093</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.25684139525116</v>
+        <v>54.25684144318149</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.42043372455055</v>
+        <v>26.42043372106784</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.770514185896217</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.8194962373284973</v>
+        <v>-0.8194962374620456</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3402</v>
+        <v>3362</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>747.6554904709185</v>
+        <v>749.6392263768848</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>145</v>
+        <v>160.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.40008457481594</v>
+        <v>69.52371819958724</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.97649115946663</v>
+        <v>33.38292128837681</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.26554904709185</v>
+        <v>2.463922637688485</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.030317945490139</v>
+        <v>4.302651354526024</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3287</v>
+        <v>3402</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>廣寰科</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>746.9052389905709</v>
+        <v>747.6554904709185</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>34.3</v>
+        <v>145</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.79595463554195</v>
+        <v>55.40008458856933</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.89001154184921</v>
+        <v>15.97649136339865</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1905238990570864</v>
+        <v>1.26554904709185</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.462321892716069</v>
+        <v>-1.030317945967122</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3390</v>
+        <v>3287</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>旭軟</t>
+          <t>廣寰科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>741.0300666809601</v>
+        <v>746.9052389905709</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>28.85</v>
+        <v>34.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.87706622629356</v>
+        <v>52.79595473277337</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.64477856263374</v>
+        <v>29.89001121791126</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.103006668096013</v>
+        <v>0.1905238990570864</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.152601661031649</v>
+        <v>-0.4623218934029349</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3362</v>
+        <v>3390</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>旭軟</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>734.6392263768848</v>
+        <v>741.0300666809601</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>160.5</v>
+        <v>28.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>69.52371814186755</v>
+        <v>57.87706624940134</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>33.38292129064842</v>
+        <v>22.64477862545018</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.463922637688485</v>
+        <v>1.103006668096013</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>4.302651355956989</v>
+        <v>-0.1526016611365878</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3558</v>
+        <v>4164</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>神準</t>
+          <t>承業醫</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>727.644428583709</v>
+        <v>731.3636616659603</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>140.5</v>
+        <v>30.9</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>60.82744341048664</v>
+        <v>64.25897496219824</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>35.87268737525574</v>
+        <v>18.8775166069322</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7644428583708934</v>
+        <v>1.136366166596034</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.2109281825854276</v>
+        <v>0.3216209486190305</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3141</v>
+        <v>3558</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>晶宏</t>
+          <t>神準</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>727.3752602067897</v>
+        <v>727.644428583709</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>71.5</v>
+        <v>140.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.35826197011716</v>
+        <v>60.82744349500168</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38.857357760539</v>
+        <v>35.87268736017771</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2375260206789708</v>
+        <v>0.7644428583708934</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.616639144451708</v>
+        <v>-0.2109281837301857</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>4164</v>
+        <v>3141</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>承業醫</t>
+          <t>晶宏</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>716.3636616659603</v>
+        <v>727.3752602067897</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>30.9</v>
+        <v>71.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>64.25897461876519</v>
+        <v>54.35826198915212</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.87751659473147</v>
+        <v>38.85735781838351</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.136366166596034</v>
+        <v>0.2375260206789708</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,11 +3008,11 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.3216209490101574</v>
+        <v>-1.616639144814218</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.17223291462514</v>
+        <v>55.17223292160797</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.66846337333429</v>
+        <v>24.66846339081093</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.5787703521310001</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0636782155056924</v>
+        <v>0.0636782154866139</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3704</v>
+        <v>3317</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>尼克森</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>715.6291480474022</v>
+        <v>709.1875710529947</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>45.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.00253551333477</v>
+        <v>56.48793272001672</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>38.55600826509383</v>
+        <v>31.518176961338</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5629148047402203</v>
+        <v>0.4187571052994744</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.3789826963237579</v>
+        <v>-1.395279166873609</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3317</v>
+        <v>3373</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>尼克森</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>709.1875710529947</v>
+        <v>704.5394052263933</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>16.95</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.48793269586424</v>
+        <v>52.93715533831548</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>31.51817681907702</v>
+        <v>30.46156230931428</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4187571052994744</v>
+        <v>0.4539405226393333</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.395279166616046</v>
+        <v>0.004001434206371</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3231</v>
+        <v>3704</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>704.9871148736581</v>
+        <v>700.6291480474022</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>156</v>
+        <v>45.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.50478625578379</v>
+        <v>57.0025355467758</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.45009488257043</v>
+        <v>38.55600834044128</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4987114873658072</v>
+        <v>0.5629148047402203</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.714928161274024</v>
+        <v>-0.3789826965813296</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3373</v>
+        <v>3515</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>704.5394052263933</v>
+        <v>692.0408041767037</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>16.95</v>
+        <v>250</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.93715513604188</v>
+        <v>55.06743213062833</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>30.4615623254724</v>
+        <v>15.53141153075442</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4539405226393333</v>
+        <v>0.7040804176703613</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0040014343303849</v>
+        <v>-0.5516191612914714</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>3515</v>
+        <v>3231</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>692.0408041767037</v>
+        <v>689.9871148736581</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.06743214755012</v>
+        <v>50.50478623658853</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.53141142424834</v>
+        <v>20.4500948414283</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7040804176703613</v>
+        <v>0.4987114873658072</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.5516191604328453</v>
+        <v>-1.714928161655583</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3675</v>
+        <v>3673</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>德微</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>685.4575200428045</v>
+        <v>688.1603527828262</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>311</v>
+        <v>79.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.81531078878768</v>
+        <v>52.2812919950817</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>37.83067072064043</v>
+        <v>34.73157450924427</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.045752004280445</v>
+        <v>0.3160352782826224</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-11.73538173222399</v>
+        <v>-1.65872176148511</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>新晶投控</t>
+          <t>永信</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>678.9790624420974</v>
+        <v>687.7724140946626</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>16.2</v>
+        <v>57.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.73843320666806</v>
+        <v>64.23193789153089</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.52052142315781</v>
+        <v>36.45579127555354</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3979062442097462</v>
+        <v>0.7772414094662676</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0856385446570179</v>
+        <v>0.09591468951768441</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3673</v>
+        <v>3675</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>德微</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>678.1603527828262</v>
+        <v>685.4575200428045</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>79.8</v>
+        <v>311</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.28129198306014</v>
+        <v>49.81531077483311</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>34.73157439928508</v>
+        <v>37.83067085419711</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3160352782826224</v>
+        <v>1.045752004280445</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.658721761342015</v>
+        <v>-11.73538173251022</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3211</v>
+        <v>3713</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>新晶投控</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>674.7968931077164</v>
+        <v>678.9790624420974</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>418</v>
+        <v>16.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.31945136654448</v>
+        <v>57.7384331457021</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21.93028926314686</v>
+        <v>24.52052146521165</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4796893107716411</v>
+        <v>0.3979062442097462</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-4.737530615169796</v>
+        <v>0.0856385447524157</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3665</v>
+        <v>3211</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>674.3657332383084</v>
+        <v>674.7968931077164</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2310</v>
+        <v>418</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.17901190373824</v>
+        <v>52.31945135931187</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.61142182712592</v>
+        <v>21.93028928919643</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.436573323830836</v>
+        <v>0.4796893107716411</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-25.12491888164759</v>
+        <v>-4.737530615360624</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3705</v>
+        <v>3438</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>永信</t>
+          <t>類比科</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>672.7724140946626</v>
+        <v>662.5874876709976</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>57.2</v>
+        <v>68.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>64.23193734443015</v>
+        <v>52.17640680331881</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>36.45579109621153</v>
+        <v>41.14660112006116</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7772414094662676</v>
+        <v>0.2587487670997553</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0959146899565218</v>
+        <v>-1.285139220213373</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3438</v>
+        <v>3665</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>類比科</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>662.5874876709976</v>
+        <v>659.3657332383084</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>68.7</v>
+        <v>2310</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.17640684556265</v>
+        <v>52.17901190832441</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>41.14660113086808</v>
+        <v>19.61142193089945</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2587487670997553</v>
+        <v>1.436573323830836</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.285139220213373</v>
+        <v>-25.12491888813474</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3467</v>
+        <v>3593</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台灣精材</t>
+          <t>力銘</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>658.5275070526762</v>
+        <v>659.043215076538</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>16.95</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.59534516578837</v>
+        <v>47.77855426166611</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26.73633988621211</v>
+        <v>22.12252788397928</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3527507052676234</v>
+        <v>0.404321507653798</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.234651691274693</v>
+        <v>0.0025248615129133</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3189</v>
+        <v>3467</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台灣精材</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>655.1213629250738</v>
+        <v>658.5275070526762</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>610</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.26904246792704</v>
+        <v>48.59534514864917</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.62789772985526</v>
+        <v>26.73633986346696</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.512136292507372</v>
+        <v>0.3527507052676234</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-17.38101134923532</v>
+        <v>-1.234651691446396</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3312</v>
+        <v>3646</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>弘憶股</t>
+          <t>艾恩特</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>652.2174465934214</v>
+        <v>653.2528566910232</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>57.7</v>
+        <v>23.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>55.27656175493733</v>
+        <v>52.57253580974488</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>44.65556336249605</v>
+        <v>14.91122389438256</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.721744659342144</v>
+        <v>0.3252856691023218</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3499006555388</v>
+        <v>-0.0325909201676048</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3227</v>
+        <v>3232</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>646.3237251782432</v>
+        <v>652.7881811825722</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>216</v>
+        <v>23.25</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.23400143144406</v>
+        <v>58.4780274122503</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>27.414683959842</v>
+        <v>24.12084166279692</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6323725178243206</v>
+        <v>0.2788181182572154</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>1</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.793567580488056</v>
+        <v>0.09357396682858481</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3716</v>
+        <v>3406</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>644.3419843626905</v>
+        <v>648.6583075436582</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>34.55</v>
+        <v>662</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.28011124815271</v>
+        <v>59.69940857643877</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28.91531295598906</v>
+        <v>43.6901694528641</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9341984362690438</v>
+        <v>1.365830754365827</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0592903232229391</v>
+        <v>4.680680851349564</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3593</v>
+        <v>3227</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>力銘</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>644.043215076538</v>
+        <v>646.3237251782432</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>16.95</v>
+        <v>216</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.7785543342368</v>
+        <v>46.23400150528166</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.12252788594049</v>
+        <v>27.41468397683096</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.404321507653798</v>
+        <v>0.6323725178243206</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0025248614475142</v>
+        <v>-2.793567582109782</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3609</v>
+        <v>3189</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>三一東林</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>638.8644708792265</v>
+        <v>645.1213629250738</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>27.6</v>
+        <v>610</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.55986757837983</v>
+        <v>48.26904247400169</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.52172304748365</v>
+        <v>26.62789797864934</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.886447087922653</v>
+        <v>1.512136292507372</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.2005526178635776</v>
+        <v>-17.38101134973139</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3646</v>
+        <v>3716</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>艾恩特</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>638.2528566910232</v>
+        <v>644.3419843626905</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>23.9</v>
+        <v>34.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.57253581938787</v>
+        <v>51.28011124815271</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.91122393284271</v>
+        <v>28.91531298124205</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3252856691023218</v>
+        <v>0.9341984362690438</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0325909201580668</v>
+        <v>-0.0592903232515603</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3232</v>
+        <v>3609</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>三一東林</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>637.7881811825722</v>
+        <v>638.8644708792265</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>23.25</v>
+        <v>27.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58.47802728632988</v>
+        <v>50.55986736699924</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.12084164652797</v>
+        <v>15.52172298954391</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2788181182572154</v>
+        <v>1.886447087922653</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0935739670098374</v>
+        <v>-0.2005526179494334</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3406</v>
+        <v>3607</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>谷崧</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>633.6583075436582</v>
+        <v>628.9275017763669</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>662</v>
+        <v>16.3</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>59.69940855656365</v>
+        <v>54.93389852025319</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>43.69016947223088</v>
+        <v>25.78474668167421</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.365830754365827</v>
+        <v>0.3927501776366804</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>4.680680853066647</v>
+        <v>-0.036496692655077</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3607</v>
+        <v>3702</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>谷崧</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>628.9275017763669</v>
+        <v>627.9736928740189</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>16.3</v>
+        <v>105</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.93389846277265</v>
+        <v>40.11588361016258</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25.78474653625452</v>
+        <v>37.49051811496914</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3927501776366804</v>
+        <v>1.297369287401885</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0364966925787603</v>
+        <v>-2.24444836193039</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3702</v>
+        <v>3312</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>弘憶股</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>627.9736928740189</v>
+        <v>627.2174465934214</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>105</v>
+        <v>57.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.115883633819</v>
+        <v>55.27656176322041</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37.4905181091622</v>
+        <v>44.65556340621144</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.297369287401885</v>
+        <v>0.721744659342144</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,11 +4333,11 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-2.244448362006706</v>
+        <v>-0.3499006558249942</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>58.8276904112227</v>
+        <v>58.82769042152581</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>37.87200624166599</v>
+        <v>37.87200631338305</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.005611537183797</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.5905334700343365</v>
+        <v>-0.5905334702632974</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.61335432359415</v>
+        <v>47.61335434865611</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>27.92306318184986</v>
+        <v>27.92306334495761</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.242524151778115</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.9741637369284032</v>
+        <v>-0.974163737195512</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.89654084537074</v>
+        <v>41.89654085530175</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.2640773631618</v>
+        <v>27.26407743726218</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6446328803703165</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-6.673762837789157</v>
+        <v>-6.673762838285184</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3628</v>
+        <v>3465</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>盈正</t>
+          <t>進泰電子</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>603.826365866715</v>
+        <v>607.2419157257011</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>71.3</v>
+        <v>32.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>55.12442295637802</v>
+        <v>56.80987700888891</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.78720828801125</v>
+        <v>37.96166724044026</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3826365866714987</v>
+        <v>0.2241915725701047</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2232420539208786</v>
+        <v>0.5783507865424822</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3564</v>
+        <v>3628</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>其陽</t>
+          <t>盈正</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>597.851320202944</v>
+        <v>603.826365866715</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>47.2</v>
+        <v>71.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.21620985968105</v>
+        <v>55.12442299523997</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32.51213107971767</v>
+        <v>22.78720832956466</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2851320202943931</v>
+        <v>0.3826365866714987</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.61723814944484</v>
+        <v>0.2232420538636323</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3305</v>
+        <v>3564</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>其陽</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>595.1670008583158</v>
+        <v>597.851320202944</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>144.5</v>
+        <v>47.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.65350436949488</v>
+        <v>50.21620992634537</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>32.03607199126241</v>
+        <v>32.51213119511198</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.516700085831582</v>
+        <v>0.2851320202943931</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,11 +4651,11 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-3.371063858899163</v>
+        <v>-0.6172381500363047</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.96894638343841</v>
+        <v>51.96894650325015</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>52.54930955617684</v>
+        <v>52.54930963629912</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.2967986889102824</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2312749396987024</v>
+        <v>-0.2312749399562814</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.53559958290723</v>
+        <v>50.53559961030543</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.07034829657463</v>
+        <v>17.07034832677209</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.2771623293020573</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1885606743257317</v>
+        <v>-0.1885606744879046</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3465</v>
+        <v>3265</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>進泰電子</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>592.2419157257011</v>
+        <v>592.1871654412962</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>32.1</v>
+        <v>179</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>56.80987690054841</v>
+        <v>50.18977341513245</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>37.96166725010702</v>
+        <v>18.96482718591768</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2241915725701047</v>
+        <v>0.7187165441296162</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.5783507870194693</v>
+        <v>-2.21455754991578</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3265</v>
+        <v>3672</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>康聯訊</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>592.1871654412962</v>
+        <v>590.9239934999625</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>179</v>
+        <v>11.85</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.18977337701089</v>
+        <v>55.04328160949844</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>18.96482699476838</v>
+        <v>12.88665154041291</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7187165441296162</v>
+        <v>1.092399349996246</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,11 +4863,11 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.214557549343403</v>
+        <v>0.1250534795565991</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.56739395962103</v>
+        <v>45.56739396549346</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.67432161639734</v>
+        <v>18.67432171886197</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.2780340429978853</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.536577789455238</v>
+        <v>-1.53657778977959</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.80493986510249</v>
+        <v>48.8049398394072</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>34.16618554078619</v>
+        <v>34.16618554314287</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.2740641470417644</v>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3615</v>
+        <v>3305</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>安可</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>583.195686137477</v>
+        <v>585.1670008583158</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>49.65</v>
+        <v>144.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.41210754886833</v>
+        <v>51.65350441081063</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45.04864223867495</v>
+        <v>32.03607197067052</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3195686137476961</v>
+        <v>0.516700085831582</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.6548216115150387</v>
+        <v>-3.371063859624198</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3169</v>
+        <v>3615</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>亞信</t>
+          <t>安可</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>582.3214504509278</v>
+        <v>583.195686137477</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>107</v>
+        <v>49.65</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.55248240924674</v>
+        <v>54.4121075579088</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>26.2490535101883</v>
+        <v>45.04864227049001</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2321450450927766</v>
+        <v>0.3195686137476961</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.025302398127738</v>
+        <v>-0.6548216115818164</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3135</v>
+        <v>3169</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>亞信</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>578.1916238567482</v>
+        <v>582.3214504509278</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>192.5</v>
+        <v>107</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.70599392943027</v>
+        <v>44.55248244593937</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>30.68694896637428</v>
+        <v>26.24905360014825</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8191623856748166</v>
+        <v>0.2321450450927766</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-8.286282054382953</v>
+        <v>-2.025302398757366</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3207</v>
+        <v>3266</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>耀勝</t>
+          <t>昇陽</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>577.1670547104741</v>
+        <v>579.2114495119772</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>56.68216360167239</v>
+        <v>54.15476745899778</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.92843260552915</v>
+        <v>21.38068952340136</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.716705471047406</v>
+        <v>0.4211449511977218</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.2234115840675845</v>
+        <v>0.0868091996250694</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>3672</v>
+        <v>3135</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>康聯訊</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>575.9239934999625</v>
+        <v>578.1916238567482</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>11.85</v>
+        <v>192.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>55.0432814026823</v>
+        <v>43.70599391362588</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.88665159491421</v>
+        <v>30.68694892080225</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.092399349996246</v>
+        <v>0.8191623856748166</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1250534795184397</v>
+        <v>-8.28628205402044</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3498</v>
+        <v>3207</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>陽程</t>
+          <t>耀勝</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>575.5828040799227</v>
+        <v>577.1670547104741</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>121</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.78330001387732</v>
+        <v>56.68216375445448</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>30.42585295798131</v>
+        <v>22.92843269370692</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5582804079922674</v>
+        <v>1.716705471047406</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-5.270706652204317</v>
+        <v>0.2234115833997991</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>3504</v>
+        <v>3498</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>573.2368898935797</v>
+        <v>575.5828040799227</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>74.7</v>
+        <v>121</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.729614552604</v>
+        <v>45.78330003668702</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>32.02590866704171</v>
+        <v>30.42585313305287</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.323688989357963</v>
+        <v>0.5582804079922674</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,11 +5340,11 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.134603434153269</v>
+        <v>-5.27070665255727</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.71500628407288</v>
+        <v>47.71500628919789</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>42.84046327283613</v>
+        <v>42.84046338871871</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.3020219564540598</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-5.18023791208987</v>
+        <v>-5.180237912376082</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3167</v>
+        <v>3388</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大量</t>
+          <t>崇越電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>566.912682374088</v>
+        <v>563.8698224152463</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>806</v>
+        <v>93.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,49 +5428,49 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.55129618962063</v>
+        <v>44.29192684984719</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.89947727108808</v>
+        <v>27.05923705259294</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.691268237408811</v>
+        <v>0.3869822415246273</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-9.787563899148346</v>
+        <v>-1.755049572948442</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3266</v>
+        <v>3504</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>昇陽</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>564.2114495119772</v>
+        <v>563.2368898935797</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.2</v>
+        <v>74.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>54.15476747127812</v>
+        <v>48.72961457161407</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.38068947648214</v>
+        <v>32.02590889541867</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4211449511977218</v>
+        <v>0.323688989357963</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0868091996632273</v>
+        <v>-1.134603434487173</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3388</v>
+        <v>3450</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>崇越電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>563.8698224152463</v>
+        <v>560.4398709697448</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>93.7</v>
+        <v>461</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.29192683763456</v>
+        <v>50.61389861159057</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.05923660304176</v>
+        <v>31.74426838066711</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3869822415246273</v>
+        <v>0.5439870969744844</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.75504957273857</v>
+        <v>-11.52174885697058</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3450</v>
+        <v>3419</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>譁裕</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>560.4398709697448</v>
+        <v>559.9527909440824</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>461</v>
+        <v>14.45</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.61389858327959</v>
+        <v>52.82325621517383</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>31.74426835255633</v>
+        <v>17.30923198222078</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5439870969744844</v>
+        <v>0.9952790944082454</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-11.52174885420408</v>
+        <v>0.08657652218914789</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3419</v>
+        <v>3531</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>譁裕</t>
+          <t>先益</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>559.9527909440824</v>
+        <v>558.9874482401656</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14.45</v>
+        <v>22.6</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>52.82325613808786</v>
+        <v>51.41408101313026</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.30923188366469</v>
+        <v>9.163775016550009</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9952790944082454</v>
+        <v>2.398744824016563</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.086576522294084</v>
+        <v>0.0362498095609741</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3531</v>
+        <v>3416</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>先益</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>558.9874482401656</v>
+        <v>558.2266021728339</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>22.6</v>
+        <v>174</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.41408101393807</v>
+        <v>49.989175174385</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9.163775102514837</v>
+        <v>22.1903563046208</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2.398744824016563</v>
+        <v>0.3226602172833852</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,51 +5711,51 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0362498095418932</v>
+        <v>-1.899328684746349</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3416</v>
+        <v>3454</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>晶睿</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>558.2266021728339</v>
+        <v>557.0019073817281</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>174</v>
+        <v>97.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G100" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.98917521864716</v>
+        <v>25.86924695763733</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.19035622945595</v>
+        <v>56.49424332546232</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3226602172833852</v>
+        <v>0.7001907381728056</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,64 +5764,64 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.89932868455558</v>
+        <v>-0.2741254001596348</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>3454</v>
+        <v>3167</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>晶睿</t>
+          <t>大量</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>557.0019073817281</v>
+        <v>551.912682374088</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>97.3</v>
+        <v>806</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G101" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>25.86922170639414</v>
+        <v>49.55129619613471</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>56.49413479308309</v>
+        <v>29.89947738615315</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7001907381728056</v>
+        <v>1.691268237408811</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2741253158101384</v>
+        <v>-9.787563899987866</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.23335064571148</v>
+        <v>47.23335063691449</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.12115401445437</v>
+        <v>18.12115411127939</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.063037111915066</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>29.16947174145665</v>
+        <v>29.16947173725917</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.81875900087869</v>
+        <v>46.81875899880467</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.85093628019992</v>
+        <v>12.85093624599512</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.6706670735285751</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.55118079622306</v>
+        <v>48.55118081385132</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.38437461555738</v>
+        <v>15.38437467742162</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.5590075988115158</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-8.419652982628373</v>
+        <v>-8.419652987970489</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.23085429336442</v>
+        <v>49.23085431059038</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.90154396081771</v>
+        <v>14.90154409040471</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.4409224103958409</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.032124146737364</v>
+        <v>-1.032124147138031</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.36522475449235</v>
+        <v>43.36522479441859</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.15171946421498</v>
+        <v>30.15171952417795</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.5251259633293426</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.129924852849025</v>
+        <v>-1.129924853154293</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.13220466004428</v>
+        <v>40.13220469872719</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.1103090311933</v>
+        <v>23.11030928318624</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.2258145875330612</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.34025309071599</v>
+        <v>-1.340253091126203</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>3706</v>
+        <v>4119</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>525.2636049548773</v>
+        <v>525.4626835859415</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>85.5</v>
+        <v>41.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.35623410376426</v>
+        <v>41.97493745200886</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.07017842124936</v>
+        <v>23.42017917157976</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5263604954877297</v>
+        <v>0.5462683585941539</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.7149865241511746</v>
+        <v>0.3951384894900169</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4137</v>
+        <v>3706</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>麗豐-KY</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>518.854325298009</v>
+        <v>525.2636049548773</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>109</v>
+        <v>85.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>54.19902897439967</v>
+        <v>47.35623410987358</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>26.59296547658748</v>
+        <v>18.07017857979624</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3854325298009002</v>
+        <v>0.5263604954877297</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.3652801499638232</v>
+        <v>-0.7149865243801314</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>3526</v>
+        <v>4137</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>凡甲</t>
+          <t>麗豐-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>513.1091679575195</v>
+        <v>518.854325298009</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>323</v>
+        <v>109</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.59773719681464</v>
+        <v>54.19902907924071</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>27.67206580785322</v>
+        <v>26.59296560477348</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3109167957519485</v>
+        <v>0.3854325298009002</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-9.087924719470715</v>
+        <v>0.3652801493914502</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>4119</v>
+        <v>3526</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>510.4626835859415</v>
+        <v>513.1091679575195</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>41.6</v>
+        <v>323</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.974937347947</v>
+        <v>37.59773721855437</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.42017921204123</v>
+        <v>27.67206607205696</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5462683585941539</v>
+        <v>0.3109167957519485</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.395138489795285</v>
+        <v>-9.087924721283272</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3491</v>
+        <v>3512</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>皇龍</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>500.5190573596621</v>
+        <v>512.5886734965686</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>1690</v>
+        <v>20.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.45608018733216</v>
+        <v>53.20546007136984</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.17515454791136</v>
+        <v>25.32025119223637</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.051905735966211</v>
+        <v>0.7588673496568588</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-54.76012709903874</v>
+        <v>0.0658647593401322</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3527</v>
+        <v>3491</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>聚積</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>500.0807244540297</v>
+        <v>500.5190573596621</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>59.4</v>
+        <v>1690</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.25202329944757</v>
+        <v>42.45608018218736</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>23.91564793422348</v>
+        <v>21.17515460167576</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5080724454029666</v>
+        <v>1.051905735966211</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0639409384187969</v>
+        <v>-54.7601271009469</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3512</v>
+        <v>3630</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>皇龍</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>497.5886734965686</v>
+        <v>500.4951852922438</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>20.8</v>
+        <v>29.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>53.20545988437196</v>
+        <v>55.26989363566203</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>25.32025114515308</v>
+        <v>19.38585418001296</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7588673496568588</v>
+        <v>1.049518529224376</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0658647594259929</v>
+        <v>0.3811133006090178</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3209</v>
+        <v>3527</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>496.7549935760458</v>
+        <v>500.0807244540297</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>61.2</v>
+        <v>59.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.02139702930004</v>
+        <v>51.25202329944757</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>34.50487783896691</v>
+        <v>23.91564796214992</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.675499357604576</v>
+        <v>0.5080724454029666</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.842819474970176</v>
+        <v>-0.06394093881946621</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3372</v>
+        <v>3209</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>典範</t>
+          <t>全科</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>493.9667252668116</v>
+        <v>496.7549935760458</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19.7</v>
+        <v>61.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.72854986152054</v>
+        <v>39.02139703085267</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.19676865154078</v>
+        <v>34.50487784911488</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.396672526681157</v>
+        <v>0.675499357604576</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2768544084260161</v>
+        <v>-2.842819475056041</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>3596</v>
+        <v>3372</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>典範</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>492.6220549883165</v>
+        <v>493.9667252668116</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>182.5</v>
+        <v>19.7</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.89361621206403</v>
+        <v>44.72854975166741</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>20.26290868921397</v>
+        <v>16.19676851905539</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7622054988316435</v>
+        <v>0.396672526681157</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.25329682304111</v>
+        <v>-0.2768544083210815</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>3661</v>
+        <v>3596</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>492.3562985540229</v>
+        <v>492.6220549883165</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>4105</v>
+        <v>182.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.7508647007716</v>
+        <v>48.89361586536454</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20.33522857803367</v>
+        <v>20.2629090950938</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7356298554022872</v>
+        <v>0.7622054988316435</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-93.0585632270495</v>
+        <v>-1.253296819129847</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3583</v>
+        <v>3661</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>485.8035489766211</v>
+        <v>492.3562985540229</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>803</v>
+        <v>4105</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.51802723903088</v>
+        <v>43.75086469786375</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>25.97247103648515</v>
+        <v>20.33522876957213</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5803548976621132</v>
+        <v>0.7356298554022872</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-16.30805214206016</v>
+        <v>-93.05856324612968</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3630</v>
+        <v>3583</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>485.4951852922438</v>
+        <v>485.8035489766211</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>29.1</v>
+        <v>803</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>55.26989359601094</v>
+        <v>46.51802725127192</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.38585407824345</v>
+        <v>25.97247122576782</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.049518529224376</v>
+        <v>0.5803548976621132</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,11 +6824,11 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.3811133007330354</v>
+        <v>-16.30805214368189</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.15627724820785</v>
+        <v>38.15627729654657</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.47877250136306</v>
+        <v>20.47877272991412</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.3744095934875733</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-2.305693627648767</v>
+        <v>-2.305693628583663</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.84355223872896</v>
+        <v>46.84355226283195</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>42.42363168607316</v>
+        <v>42.42363185118884</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.8490142850113472</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.09357139681913471</v>
+        <v>-0.0935713968668339</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>468.1275130032444</v>
+        <v>483.1275130032444</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>18.35</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>36.99893437865132</v>
+        <v>36.99893935032395</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>44.86122023061171</v>
+        <v>44.86122270263846</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.3127513003244374</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.3271855053319585</v>
+        <v>0.3271855016114666</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3645</v>
+        <v>4155</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>訊映</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>467.3332641473361</v>
+        <v>481.3448096563467</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>15.05</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.12808355688212</v>
+        <v>56.00691583576626</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>20.87574663264459</v>
+        <v>28.53165386596831</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2333264147336094</v>
+        <v>0.6344809656346744</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-2.429921631129411</v>
+        <v>-0.0032414466761266</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4155</v>
+        <v>3521</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>訊映</t>
+          <t>鴻翊</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>466.3448096563467</v>
+        <v>479.5574352056887</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>15.05</v>
+        <v>12.65</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>56.00691578572291</v>
+        <v>47.69789057408564</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>28.53165386596831</v>
+        <v>20.6078773813104</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6344809656346744</v>
+        <v>0.4557435205688664</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0032414466188883</v>
+        <v>0.1009965842868174</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3521</v>
+        <v>3645</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>鴻翊</t>
+          <t>達邁</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>464.5574352056887</v>
+        <v>477.3332641473361</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>12.65</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.69789061734676</v>
+        <v>39.12808356518966</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>20.60787732827562</v>
+        <v>20.87574694044123</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4557435205688664</v>
+        <v>0.2333264147336094</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1009965843154356</v>
+        <v>-2.429921631635013</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3444</v>
+        <v>3484</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>利機</t>
+          <t>崧騰</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>453.5636765885591</v>
+        <v>465.6898917786995</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>45.75</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.65387317431024</v>
+        <v>58.079411120951</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>27.81136883054461</v>
+        <v>14.00084028852854</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3563676588559123</v>
+        <v>1.068989177869948</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-2.410534196558207</v>
+        <v>0.2590810867777667</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3484</v>
+        <v>3444</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>崧騰</t>
+          <t>利機</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>450.6898917786995</v>
+        <v>453.5636765885591</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>45.75</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>58.07941098603127</v>
+        <v>45.65387318753972</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14.00084029700926</v>
+        <v>27.81136894991874</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.068989177869948</v>
+        <v>0.3563676588559123</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,11 +7248,11 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.2590810870830432</v>
+        <v>-2.41053419682533</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>51.26967680190257</v>
+        <v>51.26967684898292</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>20.2955057797152</v>
+        <v>20.29550579377375</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.7854152098091933</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0900689494166951</v>
+        <v>0.0900689488633937</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>44.10832005912413</v>
+        <v>44.10832012883835</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>21.8805558371864</v>
+        <v>21.88055592259065</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.5551449947543152</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.3816979422691691</v>
+        <v>-0.3816979424313438</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>48.21864833349748</v>
+        <v>48.21864837597111</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>20.93557612246698</v>
+        <v>20.93557613059345</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5303804629105834</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.140716789205208</v>
+        <v>-0.1407167895200191</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>50.09568647283816</v>
+        <v>50.09568658278693</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>24.6605706587296</v>
+        <v>24.66057070970288</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.5199493927153362</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.009872180984320401</v>
+        <v>0.009872180898464001</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>39.83834302400627</v>
+        <v>39.83834298985611</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>25.71770278015245</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-52.04792706493909</v>
+        <v>-52.0479270668465</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>48.84792702322574</v>
+        <v>48.84792701075818</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>31.10907116118965</v>
+        <v>31.10907117786615</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.4967769781795502</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-1.019722587464962</v>
+        <v>-1.019722587436337</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3701</v>
+        <v>3413</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>430.771417678874</v>
+        <v>431.2205190876666</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>47.9</v>
+        <v>307.5</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,49 +7601,49 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>34.25515270677397</v>
+        <v>47.24353796853984</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>25.39292240144345</v>
+        <v>11.17587868294186</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.5771417678873964</v>
+        <v>0.6220519087666554</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M135" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.6926513980771394</v>
+        <v>-2.654097767057696</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3715</v>
+        <v>3701</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>430.2181721505834</v>
+        <v>430.771417678874</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>166.5</v>
+        <v>47.9</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45.32238265036246</v>
+        <v>34.25515272051102</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.95066077959647</v>
+        <v>25.39292253994403</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.5218172150583444</v>
+        <v>0.5771417678873964</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.7511293625363962</v>
+        <v>-0.6926513982870102</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3545</v>
+        <v>3715</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>429.3678855316816</v>
+        <v>430.2181721505834</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>53.9</v>
+        <v>166.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>44.90635820468815</v>
+        <v>45.32238266196723</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23.79828808208924</v>
+        <v>12.95066088173016</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.4367885531681648</v>
+        <v>0.5218172150583444</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.940720914017842</v>
+        <v>-0.7511293628225788</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>4104</v>
+        <v>3545</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>423.3921433244809</v>
+        <v>429.3678855316816</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>69.7</v>
+        <v>53.9</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.67978750051533</v>
+        <v>44.9063582243539</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>27.0097339747225</v>
+        <v>23.79828815991792</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.839214332448092</v>
+        <v>0.4367885531681648</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.1218345573929586</v>
+        <v>-0.9407209143612728</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3533</v>
+        <v>4104</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>419.9782732199939</v>
+        <v>423.3921433244809</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>2240</v>
+        <v>69.7</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>41.23444275830656</v>
+        <v>40.67978757734882</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>20.6192965777398</v>
+        <v>27.00973394897306</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.4978273219993839</v>
+        <v>0.839214332448092</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,11 +7831,11 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-47.45674102771617</v>
+        <v>0.1218345572021749</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.42222931588068</v>
+        <v>44.42222928385229</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>13.71927701008061</v>
+        <v>13.71927710847963</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.4073051837915675</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.7233617479050864</v>
+        <v>-0.7233617480195548</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>54.97657602216356</v>
+        <v>54.97657615833218</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>10.54961214526874</v>
+        <v>10.54961215324151</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.7471430759698224</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.018220876950999</v>
+        <v>0.0182208769032996</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3413</v>
+        <v>3709</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>416.2205190876666</v>
+        <v>413.5388456460719</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>307.5</v>
+        <v>73.3</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,49 +7972,49 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>47.24353791293301</v>
+        <v>35.339583731649</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>11.17587861445806</v>
+        <v>30.58297408445239</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.6220519087666554</v>
+        <v>0.3538845646071879</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-2.654097765340564</v>
+        <v>-2.071880262574718</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3709</v>
+        <v>3631</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>鑫聯大投控</t>
+          <t>晟楠</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>413.5388456460719</v>
+        <v>412.2566680723209</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>73.3</v>
+        <v>33.95</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>35.33958382550806</v>
+        <v>41.62489970755928</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>30.58297422644585</v>
+        <v>27.80449572369734</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.3538845646071879</v>
+        <v>0.7256668072320911</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-2.07188026310895</v>
+        <v>-0.489025060583516</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>3631</v>
+        <v>4142</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>晟楠</t>
+          <t>國光生</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>412.2566680723209</v>
+        <v>411.2864566103269</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>33.95</v>
+        <v>17.65</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>41.6248996789663</v>
+        <v>51.47524318696972</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>27.80449572369734</v>
+        <v>9.99095809811072</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.7256668072320911</v>
+        <v>0.62864566103269</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.4890250604690356</v>
+        <v>0.06836019280251431</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3501</v>
+        <v>3533</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>維熹</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>407.1847797967059</v>
+        <v>409.9782732199939</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>42.2</v>
+        <v>2240</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>48.66111717990046</v>
+        <v>41.23444279056754</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>23.7354737856961</v>
+        <v>20.61929663666327</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.7184779796705865</v>
+        <v>0.4978273219993839</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.3282774544144685</v>
+        <v>-47.45674103343993</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3323</v>
+        <v>3632</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>加百裕</t>
+          <t>研勤</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>402.4975842960332</v>
+        <v>407.4291035472118</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>34.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>41.26014928464592</v>
+        <v>49.98926679863126</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>26.2107343518054</v>
+        <v>12.42632893601634</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.2497584296033207</v>
+        <v>0.2429103547211759</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.5575449113245723</v>
+        <v>0.0349324700638949</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3551</v>
+        <v>3501</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>維熹</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>399.9624087254729</v>
+        <v>407.1847797967059</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>193</v>
+        <v>42.2</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>44.93087355975195</v>
+        <v>48.66111716566441</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>16.87827317366834</v>
+        <v>23.73547382486568</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.4962408725472914</v>
+        <v>0.7184779796705865</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-3.022338753712242</v>
+        <v>0.3282774542236724</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>3432</v>
+        <v>3323</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>加百裕</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>399.3365692369534</v>
+        <v>402.4975842960332</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>18.7</v>
+        <v>34.05</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>49.05020629523354</v>
+        <v>41.26014938629613</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>17.54323519600855</v>
+        <v>26.210734652017</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.9336569236953376</v>
+        <v>0.2497584296033207</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0422806523596566</v>
+        <v>-0.5575449117157013</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>4142</v>
+        <v>3551</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>國光生</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>396.2864566103269</v>
+        <v>399.9624087254729</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>17.65</v>
+        <v>193</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>51.4752430968449</v>
+        <v>44.93087361056652</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>9.990958066318033</v>
+        <v>16.87827335256988</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.62864566103269</v>
+        <v>0.4962408725472914</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>1</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.06836019283113209</v>
+        <v>-3.022338754628052</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>3680</v>
+        <v>3432</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>台端</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>396.1060788243379</v>
+        <v>399.3365692369534</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>503</v>
+        <v>18.7</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,13 +8396,13 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45.60286139258705</v>
+        <v>49.05020631749027</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>15.89413826642959</v>
+        <v>17.5432352283604</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.6106078824337891</v>
+        <v>0.9336569236953376</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>1</v>
@@ -8414,31 +8414,31 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-9.178958876389132</v>
+        <v>-0.0422806524645954</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>3580</v>
+        <v>3680</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>友威科</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>394.3185380338967</v>
+        <v>396.1060788243379</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>94.3</v>
+        <v>503</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,16 +8449,16 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>44.71734550784631</v>
+        <v>45.60286142071367</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>19.83652747392322</v>
+        <v>15.89413845950157</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.4318538033896708</v>
+        <v>0.6106078824337891</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-2.209480203256242</v>
+        <v>-9.178958879728004</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>3714</v>
+        <v>3580</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>友威科</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>393.5469936896989</v>
+        <v>394.3185380338967</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,16 +8502,16 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>42.9619867779605</v>
+        <v>44.71734561794388</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>19.47012993845168</v>
+        <v>19.83652763774086</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.3546993689698893</v>
+        <v>0.4318538033896708</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-1.367621904147272</v>
+        <v>-2.209480203809548</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3632</v>
+        <v>3714</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>研勤</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>392.4291035472118</v>
+        <v>393.5469936896989</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,16 +8555,16 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>49.98926679863126</v>
+        <v>42.96198675532303</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>12.42632893601634</v>
+        <v>19.47012995251302</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.2429103547211759</v>
+        <v>0.3546993689698893</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
@@ -8573,11 +8573,11 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.0349324700638949</v>
+        <v>-1.367621904051866</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>39.71232612403741</v>
+        <v>39.71232613125397</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>29.70285881800481</v>
+        <v>29.70285905766851</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.1943938148505533</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-1.163613573617208</v>
+        <v>-1.163613573722144</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>48.72861968545273</v>
+        <v>48.72861974285724</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>13.51555357275829</v>
+        <v>13.51555373762018</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.09186015678463021</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.0289779826996078</v>
+        <v>-0.0289779828236248</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>43.60951489148108</v>
+        <v>43.60951490465142</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>14.94473920808543</v>
+        <v>14.94473923210903</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.674548127786329</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-1.714328167619326</v>
+        <v>-1.714328168020023</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>48.9348677186734</v>
+        <v>48.93486778194589</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>17.7739956196543</v>
+        <v>17.77399557149185</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.5419368278140582</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-0.0384147344688779</v>
+        <v>-0.0384147346215142</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>38.10521825081902</v>
+        <v>38.10521835374525</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>31.72467990371952</v>
+        <v>31.72467994329558</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.1888925625906945</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0322421352159112</v>
+        <v>0.032242135130053</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>48.50337546685295</v>
+        <v>48.50337556789069</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>14.60928675393615</v>
+        <v>14.6092867857224</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.5232950736414423</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.0409387064660448</v>
+        <v>0.0409387063992671</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>48.1489998356883</v>
+        <v>48.14900020938408</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>29.12773047546205</v>
+        <v>29.12773050101864</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.3206491691182536</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.1415664305970774</v>
+        <v>-0.1415664318563223</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>45.22384145139344</v>
+        <v>45.22384149266448</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>26.76716346662969</v>
+        <v>26.76716358814595</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.2839204700742448</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-1.283514574938292</v>
+        <v>-1.283514575835023</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>52.67211958061463</v>
+        <v>52.6721202215764</v>
       </c>
       <c r="I162" s="2" t="n">
         <v>19.31325470588846</v>
@@ -9060,21 +9060,21 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>3272</v>
+        <v>3557</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>東碩</t>
+          <t>嘉威</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>364.0801042872155</v>
+        <v>372.3255786873725</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>16.6</v>
+        <v>26.9</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>42.44274902710811</v>
+        <v>54.35023663570164</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>18.78412585372378</v>
+        <v>19.94012700291683</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.90801042872155</v>
+        <v>2.732557868737252</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.0938068857706605</v>
+        <v>0.5137867552937467</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>3686</v>
+        <v>3272</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>達能</t>
+          <t>東碩</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>361.3872073134425</v>
+        <v>364.0801042872155</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>50.06499883595332</v>
+        <v>42.44274911638843</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15.79585636412953</v>
+        <v>18.78412590532902</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.138720731344242</v>
+        <v>1.90801042872155</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.0276686453826661</v>
+        <v>-0.0938068859042149</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>3310</v>
+        <v>3686</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>達能</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>360.397336154564</v>
+        <v>361.3872073134425</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>41.11385496735731</v>
+        <v>50.06499903110129</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>23.83663904157146</v>
+        <v>15.79585655818756</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.0397336154564018</v>
+        <v>1.138720731344242</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.615479888864243</v>
+        <v>-0.0276686453922039</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>3178</v>
+        <v>3310</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>公準</t>
+          <t>佳穎</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>359.8557901430735</v>
+        <v>360.397336154564</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>64.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,16 +9244,16 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>42.42962275335916</v>
+        <v>41.11385497023903</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>23.53390946544317</v>
+        <v>23.83663904384701</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.4855790143073509</v>
+        <v>0.0397336154564018</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.8732227442055573</v>
+        <v>-0.6154798888833327</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3557</v>
+        <v>3178</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>嘉威</t>
+          <t>公準</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>357.3255786873725</v>
+        <v>359.8557901430735</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>26.9</v>
+        <v>64.5</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>54.35023659674515</v>
+        <v>42.42962277728874</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>19.94012693939504</v>
+        <v>23.53390951087556</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>2.732557868737252</v>
+        <v>0.4855790143073509</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,11 +9315,11 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.513786755455921</v>
+        <v>-0.8732227445108173</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>44.10308169841794</v>
+        <v>44.10308175103925</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>25.45355179374133</v>
+        <v>25.45355202397252</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.6190210360940747</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.992535105694854</v>
+        <v>-0.9925351061909208</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>45.51634721169703</v>
+        <v>45.51634722653145</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>22.47514948464215</v>
+        <v>22.47514953527332</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.5268705424162556</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.9071607023064178</v>
+        <v>-0.90716070243044</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>43.97014993176512</v>
+        <v>43.97014996117729</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>18.63054930901971</v>
+        <v>18.63054950366057</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.477425317967254</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.8214349534352196</v>
+        <v>-0.8214349537595826</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9484,21 +9484,21 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>3710</v>
+        <v>3313</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>連展投控</t>
+          <t>斐成</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>344.9064738523293</v>
+        <v>348.065433192974</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>6.33</v>
+        <v>11.85</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>49.71077825671206</v>
+        <v>53.39788112020937</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>13.40451829981246</v>
+        <v>21.24126079275952</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.4906473852329351</v>
+        <v>0.8065433192974026</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.0058193623720914</v>
+        <v>0.1188630958852796</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>3693</v>
+        <v>3710</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>營邦</t>
+          <t>連展投控</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>344.2141993234135</v>
+        <v>344.9064738523293</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>501</v>
+        <v>6.33</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>38.60203418010136</v>
+        <v>49.71077831275331</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>14.67273972322167</v>
+        <v>13.40451829295362</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.4214199323413521</v>
+        <v>0.4906473852329351</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-10.04987143182411</v>
+        <v>-0.0058193624293293</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>3297</v>
+        <v>3693</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>杭特</t>
+          <t>營邦</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>343.4994134883696</v>
+        <v>344.2141993234135</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>30.9</v>
+        <v>501</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>45.34751680316635</v>
+        <v>38.60203420418864</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>20.41225877930087</v>
+        <v>14.67273974466936</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.3499413488369531</v>
+        <v>0.4214199323413521</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.0212176525604174</v>
+        <v>-10.0498714351631</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>3563</v>
+        <v>3297</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>杭特</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>342.3776430345897</v>
+        <v>343.4994134883696</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>706</v>
+        <v>30.9</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,49 +9668,49 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>34.27653212272513</v>
+        <v>45.34751689496344</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>28.32214304403761</v>
+        <v>20.41225874994415</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.2377643034589691</v>
+        <v>0.3499413488369531</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-16.62025646857398</v>
+        <v>0.0212176519021735</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3228</v>
+        <v>3563</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>金麗科</t>
+          <t>牧德</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>338.7663765384173</v>
+        <v>342.3776430345897</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>160.5</v>
+        <v>706</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,25 +9721,25 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>35.16031518654101</v>
+        <v>34.27653213741981</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>21.94522440603569</v>
+        <v>28.3221432895006</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.3766376538417303</v>
+        <v>0.2377643034589691</v>
       </c>
       <c r="K175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-5.853159308087708</v>
+        <v>-16.62025647362998</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9749,21 +9749,21 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>3163</v>
+        <v>3228</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>金麗科</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>337.5875622288315</v>
+        <v>338.7663765384173</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>860</v>
+        <v>160.5</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>39.74843936814196</v>
+        <v>35.16031521152664</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>15.30361567434025</v>
+        <v>21.94522453360259</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.7587562228831471</v>
+        <v>0.3766376538417303</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-23.14215478624606</v>
+        <v>-5.853159310281863</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3339</v>
+        <v>3163</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>334.1815462794174</v>
+        <v>337.5875622288315</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>42.1</v>
+        <v>860</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,13 +9827,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>39.2720277258187</v>
+        <v>39.74843938753416</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>12.32027798922097</v>
+        <v>15.30361584572314</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.4181546279417379</v>
+        <v>0.7587562228831471</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.5836295034876631</v>
+        <v>-23.14215478901245</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>3587</v>
+        <v>3339</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>333.7105281917442</v>
+        <v>334.1815462794174</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>293</v>
+        <v>42.1</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>41.89760584923031</v>
+        <v>39.2720277347423</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>18.59613634471521</v>
+        <v>12.32027806355514</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.3710528191744185</v>
+        <v>0.4181546279417379</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-5.415013444576922</v>
+        <v>-0.5836295035639778</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3313</v>
+        <v>3587</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>斐成</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>333.065433192974</v>
+        <v>333.7105281917442</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>11.85</v>
+        <v>293</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>53.39788101580639</v>
+        <v>41.89760588848165</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>21.24126066563716</v>
+        <v>18.59613644031136</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.8065433192974026</v>
+        <v>0.3710528191744185</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
@@ -9951,11 +9951,11 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.1188630959806754</v>
+        <v>-5.415013445912458</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>39.62102598493284</v>
+        <v>39.62102601242098</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>29.00505218731413</v>
+        <v>29.00505227739276</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.2368338113283488</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.4480307779665374</v>
+        <v>-0.4480307780523954</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>42.5651260460814</v>
+        <v>42.56512599444371</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>29.21194901233108</v>
+        <v>29.21194897260829</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.2320454186946774</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.2818135357912592</v>
+        <v>-0.2818135356958602</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>44.42187552671814</v>
+        <v>44.42187536388946</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>18.93133843293145</v>
+        <v>18.93133792272962</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1.099661706002653</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-2.622175631669844</v>
+        <v>-2.622175625812437</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>47.28257070650432</v>
+        <v>47.28257070329936</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>8.429151639103736</v>
+        <v>8.429151622090945</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.7409887360303998</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.0289333518875452</v>
+        <v>-0.0289333519638623</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>43.65582813346028</v>
+        <v>43.65582824164886</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>21.42223557878225</v>
+        <v>21.42223590610624</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.7125580581035673</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-1.56947564541878</v>
+        <v>-1.569475648948478</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>36.20389689236452</v>
+        <v>36.20389733726252</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>21.06182912247824</v>
+        <v>21.06182912777277</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.4003415653317057</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0816041071098316</v>
+        <v>0.08160410698581751</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>44.93316457569961</v>
+        <v>44.93316463617884</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>30.03418067111688</v>
+        <v>30.03418084168451</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.1517007292395316</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.7314891705931026</v>
+        <v>-0.7314891708697466</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>43.10176249582205</v>
+        <v>43.10176255959615</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>17.15418942452912</v>
+        <v>17.15418944848049</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.6503915180774724</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.8243441207065225</v>
+        <v>-0.8243441218512979</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>36.57517554099893</v>
+        <v>36.57517555663019</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>24.25322065858276</v>
+        <v>24.25322076496308</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.4659892300631965</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-1.009759970448841</v>
+        <v>-1.009759970544244</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>38.22110044808536</v>
+        <v>38.22110047704697</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>27.05138072241418</v>
+        <v>27.05138084487843</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.3372061968000131</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-3.746485553364999</v>
+        <v>-3.746485554032797</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>38.07519448824498</v>
+        <v>38.07519460502294</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>25.36522167811032</v>
+        <v>25.36522175968515</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.2810166311311368</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-2.57399109670839</v>
+        <v>-2.573991097051815</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>39.54244707206844</v>
+        <v>39.54244713097631</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>24.78279540979193</v>
+        <v>24.78279550326912</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.3587122017743488</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.8156964549575721</v>
+        <v>-0.8156964551006702</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>43.06817145195644</v>
+        <v>43.06817147880768</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>16.3689974004416</v>
+        <v>16.36899737822503</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.2876689340093894</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.2305514545278456</v>
+        <v>-0.2305514545850828</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>46.25899620097917</v>
+        <v>46.25899626230116</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>15.8986850146554</v>
+        <v>15.89868509151785</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.3143576282366239</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.1053737573675032</v>
+        <v>-0.1053737574915174</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>44.90327473202983</v>
+        <v>44.90327471443872</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>18.15284488039177</v>
+        <v>18.15284491909384</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.179014636708031</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-1.066253478734548</v>
+        <v>-1.066253478820403</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>42.42553396358569</v>
+        <v>42.42553396080347</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>17.50501226613704</v>
+        <v>17.50501248568449</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.5308101406817568</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-14.75729553792923</v>
+        <v>-14.75729553974176</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>48.14764992457007</v>
+        <v>48.14764998325556</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>15.06625530621064</v>
+        <v>15.06625537347906</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.7691660620789074</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.0846230059884004</v>
+        <v>0.084623005940701</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>41.69366159618716</v>
+        <v>41.69366152631123</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>23.08003725600427</v>
+        <v>23.08003756040024</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.4191883578977422</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.2006498838792205</v>
+        <v>-0.200649883936457</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>44.60583057701275</v>
+        <v>44.60583061080227</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>18.47432567752891</v>
+        <v>18.47432579173796</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.6645531760746038</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.3377235597839018</v>
+        <v>-0.3377235599174538</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>35.71715283227554</v>
+        <v>35.71715284252731</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>18.09994445093514</v>
+        <v>18.09994460629161</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.3906317419715517</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-2.537215611584745</v>
+        <v>-2.537215611832765</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>25.58091891955088</v>
+        <v>25.58091892473327</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>56.19702741619062</v>
+        <v>56.19702752425211</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.4698244068589027</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.1134163538011666</v>
+        <v>0.1134163536962282</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>36.51070955235884</v>
+        <v>36.51070942046713</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>19.93013964381714</v>
+        <v>19.93013966775268</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.5615433417417139</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.138580781341985</v>
+        <v>-0.1385807813610657</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>47.75231133971416</v>
+        <v>47.75231136776051</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>19.63318297233713</v>
+        <v>19.63318301146056</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.2888896965395512</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.014181272999181</v>
+        <v>0.0141812729133241</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>30.87752018638819</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>14.45001938231122</v>
+        <v>14.45001946664955</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.6110011118557378</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.08560825887288789</v>
+        <v>-0.08560825918770069</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>40.75994833022396</v>
+        <v>40.75994832398345</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>15.72002598268994</v>
+        <v>15.7200260621272</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.4309376228054487</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.5411269182753111</v>
+        <v>-0.5411269184851811</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>24.94095855715646</v>
+        <v>24.94095857136793</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>20.10469623206496</v>
+        <v>20.10469635878115</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.6556034063486994</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.1994015640322315</v>
+        <v>-0.1994015641562505</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>28.20750729993891</v>
+        <v>28.20750732201584</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>20.64213567157082</v>
+        <v>20.64213563512148</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.4390144842196585</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>0.0140899045010396</v>
+        <v>0.0140899042339244</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>40.82347315582091</v>
+        <v>40.82347322134008</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>16.86426390046548</v>
+        <v>16.86426409410575</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.6039349564279939</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.7140929584419544</v>
+        <v>-0.7140929588617101</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>40.6340194157817</v>
+        <v>40.63401915749232</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>12.97504531973477</v>
+        <v>12.97504569024099</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.3351622067308653</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.005373813086235</v>
+        <v>0.0053738132674919</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>37.61943088953377</v>
+        <v>37.61943080424712</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>40.07526522643967</v>
+        <v>40.07526532162962</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.2658060636615297</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.0034904092112983</v>
+        <v>-0.0034904092208404</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>38.29171828890277</v>
+        <v>38.29171831964933</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>14.72618442507441</v>
+        <v>14.72618457714957</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.4374112238647815</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.4044448788841596</v>
+        <v>-0.4044448790081772</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>40.19673526393883</v>
+        <v>40.19673536090971</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>28.81392377375174</v>
+        <v>28.81392383644269</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.6315895564711751</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.0468721346601762</v>
+        <v>0.0468721345361607</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>39.98917153053132</v>
+        <v>39.98917154782502</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>18.55128417372471</v>
+        <v>18.55128421756534</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.6053785042591854</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.5886333331229648</v>
+        <v>-0.5886333333232958</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>47.52968414552721</v>
+        <v>47.52968422113052</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>7.693084770230529</v>
+        <v>7.693084832582556</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.8585121511437164</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.0964114539236704</v>
+        <v>0.09641145361839901</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>40.72943892186085</v>
+        <v>40.72943896910021</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>15.51094476923799</v>
+        <v>15.51094492378272</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.5771341853451215</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1401309582165612</v>
+        <v>-0.140130958435969</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>39.15936790737504</v>
+        <v>39.15936743658371</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>10.27687870046613</v>
+        <v>10.27687889895049</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.2030990374374994</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.08488746312315409</v>
+        <v>-0.0848874628560409</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>37.18417064135357</v>
+        <v>37.18417068394268</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>17.25386269501402</v>
+        <v>17.25386282890887</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.5374825944213394</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.1566891291657679</v>
+        <v>0.156689128974969</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>45.15679391890856</v>
+        <v>45.15679405201097</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>7.631630050205933</v>
+        <v>7.631630150354727</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.0124037857033626</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-1.234938621959726</v>
+        <v>-1.234938625394026</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
